--- a/ADAS_backup/ADAS_交互关系.xlsx
+++ b/ADAS_backup/ADAS_交互关系.xlsx
@@ -4988,8 +4988,8 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100F4ECDE3992A08C4AB27EAAF617A05967" ma:contentTypeVersion="12" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="3dd12f097a664388af7c7ed37b7f1677">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="455088e1-af34-4927-a3f0-bdce59540293" xmlns:ns3="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="67c07fb3e546643451b6621acfe4996e" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="文档" ma:contentTypeID="0x010100F4ECDE3992A08C4AB27EAAF617A05967" ma:contentTypeVersion="18" ma:contentTypeDescription="新建文档。" ma:contentTypeScope="" ma:versionID="7a1862a2c5bfb592d13551c3fa22cd36">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="455088e1-af34-4927-a3f0-bdce59540293" xmlns:ns3="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="0695127d08f6d47f62536280da32b892" ns2:_="" ns3:_="">
     <xsd:import namespace="455088e1-af34-4927-a3f0-bdce59540293"/>
     <xsd:import namespace="f4ecdb93-bc7f-4438-8c77-236ab96c18a9"/>
     <xsd:element name="properties">
@@ -5009,6 +5009,12 @@
                 <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:testStatus" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeClassificationStatus" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeClassificationStatusDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeLastClassified" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeCorrectedByUser" minOccurs="0"/>
+                <xsd:element ref="ns3:PrimeAutofillMeta" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -5073,6 +5079,18 @@
         <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="testStatus" ma:index="20" nillable="true" ma:displayName="Test status" ma:description="Summarizes overall test outcome so failed or mixed-result files can be found quickly." ma:internalName="testStatus">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Choice">
+          <xsd:enumeration value="Pass"/>
+          <xsd:enumeration value="Fail"/>
+          <xsd:enumeration value="Error"/>
+          <xsd:enumeration value="Skipped"/>
+          <xsd:enumeration value="Mixed"/>
+          <xsd:enumeration value="Not found"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
@@ -5087,6 +5105,33 @@
           </xsd:extension>
         </xsd:complexContent>
       </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="PrimeClassificationStatus" ma:index="21" nillable="true" ma:displayName="处理状态" ma:internalName="PrimeClassificationStatus">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimeClassificationStatusDetails" ma:index="22" nillable="true" ma:displayName="处理详细信息" ma:internalName="PrimeClassificationStatusDetails">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimeLastClassified" ma:index="23" nillable="true" ma:displayName="已处理" ma:internalName="PrimeLastClassified">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:DateTime"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimeCorrectedByUser" ma:index="24" nillable="true" ma:displayName="已更正" ma:internalName="PrimeCorrectedByUser">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Boolean"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="PrimeAutofillMeta" ma:index="25" nillable="true" ma:displayName="Autofill Meta" ma:hidden="true" ma:internalName="PrimeAutofillMeta">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -5195,6 +5240,12 @@
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="455088e1-af34-4927-a3f0-bdce59540293">
       <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     </lcf76f155ced4ddcb4097134ff3c332f>
+    <PrimeCorrectedByUser xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <testStatus xmlns="455088e1-af34-4927-a3f0-bdce59540293" xsi:nil="true"/>
+    <PrimeClassificationStatusDetails xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <PrimeClassificationStatus xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <PrimeLastClassified xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
+    <PrimeAutofillMeta xmlns="f4ecdb93-bc7f-4438-8c77-236ab96c18a9" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
 </file>
@@ -5208,7 +5259,7 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1EBBA153-C290-48C3-A1BF-835A76A05191}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9AD0AF02-9332-4E4F-8E10-864E48DFDB98}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
